--- a/Data/round1decks.xlsx
+++ b/Data/round1decks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TapMiniGame\CardLoot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A542A1D-B6AB-4D9C-AD09-3798B5C71334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2B9501-5856-4F06-B4F9-BC04959ACC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，一分，一分，二分，二分，二分，威吓，威吓，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>切磋</t>
   </si>
   <si>
@@ -74,10 +70,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，一分，一分，二分，二分，二分，偷窃，偷窃，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>流浪汉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -86,10 +78,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，一分，一分，二分，二分，二分，小鬼，小鬼，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>强手</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -98,18 +86,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，一分，一分，二分，三分，贷款，贷款，陷阱，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>红衣女人</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，一分，二分，二分，二分，勾引，勾引，魅魔，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>庄家</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -122,7 +102,27 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>一分，一分，二分，二分，三分，三分，虚张，虚张，威吓，威吓，掀桌，炸弹，炸弹，炸弹</t>
+    <t>一分，一分，一分，二分，二分，恐吓，恐吓，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，二分，二分，偷窃，偷窃，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，二分，二分，小鬼，小鬼，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，二分，三分，贷款，贷款，陷阱，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，二分，二分，二分，勾引，勾引，魅魔，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，二分，二分，三分，虚张，虚张，恐吓，恐吓，掀桌，炸弹，炸弹，炸弹</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +499,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -507,16 +507,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E3" s="1" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -524,16 +524,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
@@ -541,16 +541,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -558,16 +558,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -575,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>24</v>

--- a/Data/round1decks.xlsx
+++ b/Data/round1decks.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TapMiniGame\CardLoot\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2B9501-5856-4F06-B4F9-BC04959ACC9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF083B55-3A45-488B-9AD9-F2F22D9A5F80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="第一轮卡组" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>轮次</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -74,10 +74,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>胆小</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>强手</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -98,31 +94,31 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>灵活</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一分，一分，一分，二分，二分，恐吓，恐吓，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一分，一分，一分，二分，二分，偷窃，偷窃，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一分，一分，一分，二分，二分，小鬼，小鬼，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一分，一分，一分，二分，三分，贷款，贷款，陷阱，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>一分，一分，二分，二分，二分，勾引，勾引，魅魔，炸弹，炸弹，炸弹</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>一分，一分，二分，二分，三分，虚张，虚张，恐吓，恐吓，掀桌，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，二分，二分，贷款，贷款，陷阱，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，二分，二分，勾引，勾引，魅魔，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，一分，二分，恐吓，恐吓，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，一分，二分，小鬼，小鬼，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>一分，一分，一分，一分，二分，二分，偷窃，炸弹，炸弹，炸弹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>保守</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -499,7 +495,7 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
@@ -516,7 +512,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
@@ -530,7 +526,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>21</v>
@@ -541,16 +537,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
@@ -558,16 +554,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
@@ -575,16 +571,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
